--- a/data/mapas/Mapa_de_Carrera_Ciencia_Politica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencia_Politica.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B55, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C55, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F55, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Introducción a la Ciencia Política</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B55, "SI")/44</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Teoría Política Clásica y Medieval</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C55, "SI")/44</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Historia Política Argentina I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Sociología Política</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Teoría Política Moderna</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Historia Política Argentina II</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Sistemas Políticos Comparados</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Opinión Pública y Comunicación Política</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de la Educación</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1187,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Teoría Política Contemporánea</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1258,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Relaciones Internacionales y Política Exterior</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Políticas Públicas y Administración del Estado</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Didáctica de la Ciencia Política I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1435,14 +1489,14 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Partidos Políticos y Sistemas Electorales</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1511,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1476,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Filosofía Política Latinoamericana</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Metodología del Análisis Político</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Didáctica de la Ciencia Política II</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,17 +1629,44 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Análisis DE LAS POLÍTICAS PÚBLICAS</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>CONSTRUCCION DE LA Práctica DOCENTE</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1650,44 +1731,17 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Educación Sexual Integral</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E38" s="10">
-        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G38" s="11">
-        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>ENSEÑANZA DE LA CIENCIA Política I</t>
+          <t>Seminario de Política Latinoamericana Contemporánea</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1702,7 +1756,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1721,7 +1775,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>ENSEÑANZA DE LA CIENCIA Política II</t>
+          <t>Seminario de Movimientos Sociales y Ciudadanía</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1755,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Ética</t>
+          <t>Taller de Investigación en Ciencia Política</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1770,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1786,504 +1840,26 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>FUNDAMENTOS DE LA CIENCIA Política</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E42" s="10">
-        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G42" s="11">
-        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Gobierno y Administración Nacional Provincial y Municipal</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>HISTORIA DE LA Educación ARGENTINA</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Historia de los Movimientos Sociales</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Historia del Pensamiento Politico</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Historia Polit. y Social Lat. y Arg. Contemp</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Introducción. Ciencias. SOCIALES: Política Y JURIDICA</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Lectura Escritura y Oralidad I</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Lectura Escritura y Oralidad II</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Movimientos Pol. y Sociales Contemp</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Relaciones Internacionales</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Residencia Pedagogica</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Teoría Y Práctica Política I</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Teoría Y Práctica Política II</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Ciencia_Politica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencia_Politica.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B53, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C53, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F53, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Ciencia Política</t>
+          <t>Introducción a las ciencias sociales: Política y Jurídica</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B53, "SI")/44</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Teoría Política Clásica y Medieval</t>
+          <t>Fundamentos de la ciencia política</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C53, "SI")/44</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Historia Política Argentina I</t>
+          <t>Historia mundial contemporánea</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Sociología Política</t>
+          <t>Historia del pensamiento político</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Historia de los hechos y de las ideas económicas</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Sociología</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Antropología cultural</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lectura, escritura y oralidad 1</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Teoría Política Moderna</t>
+          <t>Pedagogía general</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Historia Política Argentina II</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1040,7 +1067,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Sistemas Políticos Comparados</t>
+          <t>Sujeto de nivel</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1055,7 +1082,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1074,7 +1101,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Opinión Pública y Comunicación Política</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1089,7 +1116,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1105,44 +1132,17 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica General</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E18" s="10">
-        <f>IF(B18="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>IF(C18="SI", "APROBADO", IF(B18="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="11">
-        <f>IF(C18="SI", "🟢 Aprobada", IF(B18="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Teoría y prática política 1</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Historia política y social latinoamericana y Argentina contemporánea</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Historia de los movimientos políticos y sociales</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Derecho constitucional</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Teoría Política Contemporánea</t>
+          <t>Economía política</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Relaciones Internacionales y Política Exterior</t>
+          <t>Didactica general</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Políticas Públicas y Administración del Estado</t>
+          <t>Lectura, escritura y oralidad 2</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Ciencia Política I</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1387,7 +1414,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1402,7 +1429,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1421,7 +1448,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1436,7 +1463,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1452,51 +1479,51 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente I</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Teoría y prática política 2</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>3° Año</t>
         </is>
       </c>
-      <c r="E29" s="10">
-        <f>IF(B29="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
-        <f>IF(C29="SI", "APROBADO", IF(B29="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
-        <f>IF(C29="SI", "🟢 Aprobada", IF(B29="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Partidos Políticos y Sistemas Electorales</t>
+          <t>Movimientos políticos y sociales</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1530,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Filosofía Política Latinoamericana</t>
+          <t>Gobierno y administración nacional, provincial y municipal</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Metodología del Análisis Político</t>
+          <t>Derecho a las relaciones internacionales</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Ciencia Política II</t>
+          <t>Epistemología y metodología de la investigación</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Construcción de la práctica docente</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Enseñanza de la ciencia política 1</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1700,7 +1727,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Ecología y ambiente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1742,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1731,17 +1758,44 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Política Latinoamericana Contemporánea</t>
+          <t>DDHH, sociedad y estado</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1810,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1775,7 +1829,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Movimientos Sociales y Ciudadanía</t>
+          <t>Taller optativo: Estrategias para el analisis del discurso político</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1844,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1806,60 +1860,414 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Investigación en Ciencia Política</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Tramo Superior / Seminarios</t>
-        </is>
-      </c>
-      <c r="E41" s="10">
-        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G41" s="11">
-        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Ética</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Psicología política y social</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Política educacional y legislación escolar / Sistema y política educativa</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Nuevas tecnologias</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Enseñanza de la ciencia política 2</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Residencia pedagógica</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Medios de comunicación y opinión publica</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Const. políticas de los pueblos originarios de America Latina y en especial Argentina</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E52" s="10">
+        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Análisis de las políticas publicas</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B42 B43 B44 B45 B46 B47 B49 B50 B51 B52 B53 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C42 C43 C44 C45 C46 C47 C49 C50 C51 C52 C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
